--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2024_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:04</t>
+    <t xml:space="preserve">2026-10-05 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,7 +570,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1136262.62</v>
+        <v>1136262.63</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1119381.62</v>
+        <v>1119381.63</v>
       </c>
     </row>
     <row r="8">
